--- a/Input_data/Sequences.xlsx
+++ b/Input_data/Sequences.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aminoroa/FLS2_Project/Input Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aminoroa/FLS2_Project/Input_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C03546D0-092E-A048-BF2C-59AE55FB3361}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E57C5BDF-5AA4-B24A-B3E6-465776FAA00C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20520" xr2:uid="{1B074C2A-12A1-9D4F-AC43-5273D806EDF7}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1822" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1812" uniqueCount="216">
   <si>
     <t>Ligand Name</t>
   </si>
@@ -681,6 +681,9 @@
   </si>
   <si>
     <t>Priming Antagonist</t>
+  </si>
+  <si>
+    <t>Pa</t>
   </si>
 </sst>
 </file>
@@ -750,7 +753,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -769,6 +772,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -782,7 +791,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -799,16 +808,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -816,6 +816,27 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1151,62 +1172,71 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C30B7E0-220D-0241-8577-B469D8A69073}">
-  <dimension ref="A1:O1048575"/>
+  <dimension ref="A1:O1048574"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="51.5" defaultRowHeight="22" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="51.5" style="2"/>
-    <col min="2" max="2" width="42.83203125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="28.33203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="28.83203125" style="2" customWidth="1"/>
     <col min="3" max="3" width="44.6640625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="30.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="35.1640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="25.6640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.83203125" style="2" customWidth="1"/>
     <col min="6" max="6" width="35" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="51.5" style="2"/>
+    <col min="7" max="7" width="32.1640625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="26.83203125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="34.5" style="2" customWidth="1"/>
+    <col min="10" max="10" width="19" style="2" customWidth="1"/>
+    <col min="11" max="11" width="33.5" style="2" customWidth="1"/>
+    <col min="12" max="12" width="29.6640625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="27.33203125" style="2" customWidth="1"/>
+    <col min="14" max="14" width="23.6640625" style="2" customWidth="1"/>
+    <col min="15" max="15" width="25" style="2" customWidth="1"/>
+    <col min="16" max="16384" width="51.5" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:15" s="15" customFormat="1" ht="23" x14ac:dyDescent="0.3">
+      <c r="A1" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="13" t="s">
         <v>174</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="13" t="s">
         <v>180</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="13" t="s">
         <v>212</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="13" t="s">
         <v>197</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="14" t="s">
         <v>202</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="L1" s="13" t="s">
         <v>203</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="M1" s="13" t="s">
         <v>204</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="N1" s="13" t="s">
         <v>205</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="O1" s="13" t="s">
         <v>182</v>
       </c>
     </row>
@@ -2471,10 +2501,10 @@
       <c r="I31" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="J31" s="8">
+      <c r="J31" s="6">
         <v>108</v>
       </c>
-      <c r="K31" s="8">
+      <c r="K31" s="6">
         <v>-2.2312805070000001</v>
       </c>
       <c r="L31" s="1">
@@ -2683,10 +2713,10 @@
       <c r="I36" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="J36" s="8">
+      <c r="J36" s="6">
         <v>5011</v>
       </c>
-      <c r="K36" s="8">
+      <c r="K36" s="6">
         <v>-0.74482462900000002</v>
       </c>
       <c r="L36" s="1">
@@ -4559,50 +4589,50 @@
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A81" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D81" s="1" t="s">
+    <row r="81" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="B81" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="C81" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D81" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="E81" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="F81" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="G81" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="H81" s="1">
+      <c r="E81" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="F81" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="G81" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="H81" s="11">
         <v>5009</v>
       </c>
-      <c r="I81" s="2" t="s">
+      <c r="I81" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="J81" s="8">
+      <c r="J81" s="12">
         <v>108</v>
       </c>
-      <c r="K81" s="8">
+      <c r="K81" s="12">
         <v>-2.2312805070000001</v>
       </c>
-      <c r="L81" s="1">
+      <c r="L81" s="11">
         <v>0.13377345500000001</v>
       </c>
-      <c r="M81" s="1">
+      <c r="M81" s="11">
         <v>0.75479903500000001</v>
       </c>
-      <c r="N81" s="1">
+      <c r="N81" s="11">
         <v>3</v>
       </c>
-      <c r="O81" s="2" t="s">
+      <c r="O81" s="10" t="s">
         <v>213</v>
       </c>
     </row>
@@ -4676,10 +4706,10 @@
       <c r="I83" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="J83" s="8">
+      <c r="J83" s="6">
         <v>161</v>
       </c>
-      <c r="K83" s="8">
+      <c r="K83" s="6">
         <v>-2.0745936789999999</v>
       </c>
       <c r="L83" s="1">
@@ -4734,877 +4764,856 @@
         <v>3</v>
       </c>
     </row>
-    <row r="85" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="B85" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="C85" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="D85" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="E85" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="F85" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="G85" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="H85" s="11" t="s">
+    <row r="85" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="B85" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="C85" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="D85" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="E85" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="F85" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="G85" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="H85" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="I85" s="11" t="s">
+      <c r="I85" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="J85" s="11" t="s">
+      <c r="J85" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="K85" s="11">
+      <c r="K85" s="8">
         <v>-2.4515511650000001</v>
       </c>
-      <c r="L85" s="11">
+      <c r="L85" s="8">
         <v>-0.35800794400000002</v>
       </c>
-      <c r="M85" s="11">
+      <c r="M85" s="8">
         <v>1.3709555999999999E-2</v>
       </c>
-      <c r="N85" s="11" t="s">
+      <c r="N85" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="O85" s="11" t="s">
+      <c r="O85" s="8" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="86" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="B86" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="C86" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="D86" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="E86" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="F86" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="G86" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="H86" s="11" t="s">
-        <v>195</v>
-      </c>
-      <c r="I86" s="11" t="s">
+    <row r="86" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="B86" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="C86" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="D86" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="E86" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="F86" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="G86" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="H86" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="I86" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="J86" s="11" t="s">
+      <c r="J86" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="K86" s="11">
-        <v>6.3914162499999998</v>
-      </c>
-      <c r="L86" s="11">
-        <v>-1.872072143</v>
-      </c>
-      <c r="M86" s="11">
-        <v>1.11E-36</v>
-      </c>
-      <c r="N86" s="11">
+      <c r="K86" s="8">
+        <v>6.5208283859999998</v>
+      </c>
+      <c r="L86" s="8">
+        <v>-2.8460292780000001</v>
+      </c>
+      <c r="M86" s="8">
+        <v>1.7400000000000001E-115</v>
+      </c>
+      <c r="N86" s="8" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="B87" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="C87" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="D87" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="E87" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="F87" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="G87" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="H87" s="8">
+        <v>94</v>
+      </c>
+      <c r="I87" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="K87" s="8">
+        <v>3.6026249990000001</v>
+      </c>
+      <c r="L87" s="8">
+        <v>-0.37685876800000001</v>
+      </c>
+      <c r="M87" s="8">
+        <v>0.33435052900000001</v>
+      </c>
+      <c r="N87" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="B88" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="C88" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="D88" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="E88" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="F88" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="G88" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="H88" s="8">
+        <v>236</v>
+      </c>
+      <c r="I88" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="K88" s="8">
+        <v>3.2337220000000001E-3</v>
+      </c>
+      <c r="L88" s="8">
+        <v>1.5605380449999999</v>
+      </c>
+      <c r="M88" s="8">
+        <v>6.3399999999999998E-10</v>
+      </c>
+      <c r="N88" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="B89" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="C89" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="D89" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="E89" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="F89" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="G89" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="H89" s="8">
+        <v>289</v>
+      </c>
+      <c r="I89" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="K89" s="8">
+        <v>4.2043162729999999</v>
+      </c>
+      <c r="L89" s="8">
+        <v>-0.93444604899999995</v>
+      </c>
+      <c r="M89" s="8">
+        <v>3.2480790000000001E-3</v>
+      </c>
+      <c r="N89" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="B90" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="C90" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="D90" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="E90" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="F90" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="G90" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="H90" s="8">
+        <v>295</v>
+      </c>
+      <c r="I90" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="K90" s="8">
+        <v>4.3938823779999998</v>
+      </c>
+      <c r="L90" s="8">
+        <v>-1.394847159</v>
+      </c>
+      <c r="M90" s="8">
+        <v>7.1099999999999997E-6</v>
+      </c>
+      <c r="N90" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="B91" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="C91" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="D91" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="E91" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="F91" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="G91" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="H91" s="8">
+        <v>468</v>
+      </c>
+      <c r="I91" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="K91" s="8">
+        <v>4.6481458550000001</v>
+      </c>
+      <c r="L91" s="8">
+        <v>-0.14598699300000001</v>
+      </c>
+      <c r="M91" s="8">
+        <v>0.743751473</v>
+      </c>
+      <c r="N91" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="B92" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="C92" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="D92" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="E92" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="F92" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="G92" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="H92" s="8">
+        <v>470</v>
+      </c>
+      <c r="I92" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="K92" s="8">
+        <v>5.4752068969999996</v>
+      </c>
+      <c r="L92" s="8">
+        <v>-6.3263396999999999E-2</v>
+      </c>
+      <c r="M92" s="8">
+        <v>0.86246237800000003</v>
+      </c>
+      <c r="N92" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="B93" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="C93" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="D93" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="E93" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="F93" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="G93" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="H93" s="8">
+        <v>1090</v>
+      </c>
+      <c r="I93" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="K93" s="8">
+        <v>6.6129784699999998</v>
+      </c>
+      <c r="L93" s="8">
+        <v>-1.8691608630000001</v>
+      </c>
+      <c r="M93" s="8">
+        <v>3.25E-8</v>
+      </c>
+      <c r="N93" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="B87" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="C87" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="D87" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="E87" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="F87" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="G87" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="H87" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="I87" s="11" t="s">
-        <v>199</v>
-      </c>
-      <c r="J87" s="11" t="s">
-        <v>200</v>
-      </c>
-      <c r="K87" s="11">
-        <v>-9.7539160999999999E-2</v>
-      </c>
-      <c r="L87" s="11">
-        <v>-0.35951275999999999</v>
-      </c>
-      <c r="M87" s="11">
-        <v>7.7863699999999999E-3</v>
-      </c>
-      <c r="N87" s="11" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="88" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="B88" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="C88" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="D88" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="E88" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="F88" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="G88" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="H88" s="11">
-        <v>94</v>
-      </c>
-      <c r="I88" s="11" t="s">
+    <row r="94" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="B94" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="C94" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="D94" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="E94" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="F94" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="G94" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="H94" s="8">
+        <v>1213</v>
+      </c>
+      <c r="I94" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="K88" s="11">
-        <v>3.6026249990000001</v>
-      </c>
-      <c r="L88" s="11">
-        <v>-0.37685876800000001</v>
-      </c>
-      <c r="M88" s="11">
-        <v>0.33435052900000001</v>
-      </c>
-      <c r="N88" s="11">
+      <c r="K94" s="8">
+        <v>4.593992364</v>
+      </c>
+      <c r="L94" s="8">
+        <v>-0.50901501000000005</v>
+      </c>
+      <c r="M94" s="8">
+        <v>0.15445488299999999</v>
+      </c>
+      <c r="N94" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="89" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="B89" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="C89" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="D89" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="E89" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="F89" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="G89" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="H89" s="11">
-        <v>236</v>
-      </c>
-      <c r="I89" s="11" t="s">
+    <row r="95" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="B95" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="C95" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="D95" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="E95" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="F95" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="G95" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="H95" s="8">
+        <v>1291</v>
+      </c>
+      <c r="I95" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="K95" s="8">
+        <v>0.65540503999999999</v>
+      </c>
+      <c r="L95" s="8">
+        <v>-0.57520305900000002</v>
+      </c>
+      <c r="M95" s="8">
+        <v>0.167361485</v>
+      </c>
+      <c r="N95" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="B96" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="C96" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="D96" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="E96" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="F96" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="G96" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="H96" s="8">
+        <v>1294</v>
+      </c>
+      <c r="I96" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="K89" s="11">
-        <v>3.2337220000000001E-3</v>
-      </c>
-      <c r="L89" s="11">
-        <v>1.5605380449999999</v>
-      </c>
-      <c r="M89" s="11">
-        <v>6.3399999999999998E-10</v>
-      </c>
-      <c r="N89" s="11">
+      <c r="K96" s="8">
+        <v>0.60402162000000004</v>
+      </c>
+      <c r="L96" s="8">
+        <v>0.79465857399999995</v>
+      </c>
+      <c r="M96" s="8">
+        <v>1.0491350000000001E-3</v>
+      </c>
+      <c r="N96" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="90" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="B90" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="C90" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="D90" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="E90" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="F90" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="G90" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="H90" s="11">
-        <v>289</v>
-      </c>
-      <c r="I90" s="11" t="s">
+    <row r="97" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="B97" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="C97" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="D97" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="E97" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="F97" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="G97" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="H97" s="8">
+        <v>1391</v>
+      </c>
+      <c r="I97" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="K90" s="11">
-        <v>4.2043162729999999</v>
-      </c>
-      <c r="L90" s="11">
-        <v>-0.93444604899999995</v>
-      </c>
-      <c r="M90" s="11">
-        <v>3.2480790000000001E-3</v>
-      </c>
-      <c r="N90" s="11">
+      <c r="K97" s="8">
+        <v>4.54108906</v>
+      </c>
+      <c r="L97" s="8">
+        <v>1.045845913</v>
+      </c>
+      <c r="M97" s="8">
+        <v>9.6011999999999996E-4</v>
+      </c>
+      <c r="N97" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="91" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="B91" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="C91" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="D91" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="E91" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="F91" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="G91" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="H91" s="11">
-        <v>295</v>
-      </c>
-      <c r="I91" s="11" t="s">
+    <row r="98" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="B98" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="C98" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="D98" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="E98" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="F98" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="G98" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="H98" s="8">
+        <v>1471</v>
+      </c>
+      <c r="I98" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="K91" s="11">
-        <v>4.3938823779999998</v>
-      </c>
-      <c r="L91" s="11">
-        <v>-1.394847159</v>
-      </c>
-      <c r="M91" s="11">
-        <v>7.1099999999999997E-6</v>
-      </c>
-      <c r="N91" s="11">
+      <c r="K98" s="8">
+        <v>3.4727631090000002</v>
+      </c>
+      <c r="L98" s="8">
+        <v>-0.34334535900000002</v>
+      </c>
+      <c r="M98" s="8">
+        <v>0.31209340200000002</v>
+      </c>
+      <c r="N98" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="92" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="B92" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="C92" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="D92" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="E92" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="F92" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="G92" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="H92" s="11">
-        <v>468</v>
-      </c>
-      <c r="I92" s="11" t="s">
+    <row r="99" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="B99" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="C99" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="D99" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="E99" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="F99" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="G99" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="H99" s="8">
+        <v>1544</v>
+      </c>
+      <c r="I99" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="K92" s="11">
-        <v>4.6481458550000001</v>
-      </c>
-      <c r="L92" s="11">
-        <v>-0.14598699300000001</v>
-      </c>
-      <c r="M92" s="11">
-        <v>0.743751473</v>
-      </c>
-      <c r="N92" s="11">
+      <c r="K99" s="8">
+        <v>2.0478127810000002</v>
+      </c>
+      <c r="L99" s="8">
+        <v>-0.50584207999999997</v>
+      </c>
+      <c r="M99" s="8">
+        <v>0.15445488299999999</v>
+      </c>
+      <c r="N99" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="93" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="B93" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="C93" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="D93" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="E93" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="F93" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="G93" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="H93" s="11">
-        <v>470</v>
-      </c>
-      <c r="I93" s="11" t="s">
+    <row r="100" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="B100" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="C100" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="D100" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="E100" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="F100" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="G100" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="H100" s="8">
+        <v>1635</v>
+      </c>
+      <c r="I100" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="K93" s="11">
-        <v>5.4752068969999996</v>
-      </c>
-      <c r="L93" s="11">
-        <v>-6.3263396999999999E-2</v>
-      </c>
-      <c r="M93" s="11">
+      <c r="K100" s="8">
+        <v>4.365137786</v>
+      </c>
+      <c r="L100" s="8">
+        <v>-0.31499556299999998</v>
+      </c>
+      <c r="M100" s="8">
+        <v>0.41762116399999999</v>
+      </c>
+      <c r="N100" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="B101" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="C101" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="D101" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="E101" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="F101" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="G101" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="H101" s="8">
+        <v>1666</v>
+      </c>
+      <c r="I101" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="K101" s="8">
+        <v>2.3021172179999998</v>
+      </c>
+      <c r="L101" s="8">
+        <v>-1.988707816</v>
+      </c>
+      <c r="M101" s="8">
+        <v>4.7900000000000002E-9</v>
+      </c>
+      <c r="N101" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="B102" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="C102" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="D102" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="E102" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="F102" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="G102" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="H102" s="8">
+        <v>1810</v>
+      </c>
+      <c r="I102" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="K102" s="8">
+        <v>4.7653295929999997</v>
+      </c>
+      <c r="L102" s="8">
+        <v>-1.7664919160000001</v>
+      </c>
+      <c r="M102" s="8">
+        <v>2.45E-9</v>
+      </c>
+      <c r="N102" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="B103" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="C103" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="D103" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="E103" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="F103" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="G103" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="H103" s="8">
+        <v>1857</v>
+      </c>
+      <c r="I103" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="K103" s="8">
+        <v>4.0173615600000003</v>
+      </c>
+      <c r="L103" s="8">
+        <v>5.0176947E-2</v>
+      </c>
+      <c r="M103" s="8">
         <v>0.86246237800000003</v>
       </c>
-      <c r="N93" s="11">
+      <c r="N103" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="94" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="B94" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="C94" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="D94" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="E94" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="F94" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="G94" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="H94" s="11">
-        <v>1090</v>
-      </c>
-      <c r="I94" s="11" t="s">
+    <row r="104" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="B104" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="C104" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="D104" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="E104" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="F104" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="G104" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="H104" s="8">
+        <v>1877</v>
+      </c>
+      <c r="I104" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="K94" s="11">
-        <v>6.6129784699999998</v>
-      </c>
-      <c r="L94" s="11">
-        <v>-1.8691608630000001</v>
-      </c>
-      <c r="M94" s="11">
-        <v>3.25E-8</v>
-      </c>
-      <c r="N94" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="B95" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="C95" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="D95" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="E95" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="F95" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="G95" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="H95" s="11">
-        <v>1213</v>
-      </c>
-      <c r="I95" s="11" t="s">
-        <v>206</v>
-      </c>
-      <c r="K95" s="11">
-        <v>4.593992364</v>
-      </c>
-      <c r="L95" s="11">
-        <v>-0.50901501000000005</v>
-      </c>
-      <c r="M95" s="11">
-        <v>0.15445488299999999</v>
-      </c>
-      <c r="N95" s="11">
+      <c r="K104" s="8">
+        <v>2.2494064869999999</v>
+      </c>
+      <c r="L104" s="8">
+        <v>-0.81070486399999997</v>
+      </c>
+      <c r="M104" s="8">
+        <v>1.3709555999999999E-2</v>
+      </c>
+      <c r="N104" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="96" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="B96" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="C96" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="D96" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="E96" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="F96" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="G96" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="H96" s="11">
-        <v>1291</v>
-      </c>
-      <c r="I96" s="11" t="s">
-        <v>207</v>
-      </c>
-      <c r="K96" s="11">
-        <v>0.65540503999999999</v>
-      </c>
-      <c r="L96" s="11">
-        <v>-0.57520305900000002</v>
-      </c>
-      <c r="M96" s="11">
-        <v>0.167361485</v>
-      </c>
-      <c r="N96" s="11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="97" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="B97" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="C97" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="D97" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="E97" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="F97" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="G97" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="H97" s="11">
-        <v>1294</v>
-      </c>
-      <c r="I97" s="11" t="s">
-        <v>206</v>
-      </c>
-      <c r="K97" s="11">
-        <v>0.60402162000000004</v>
-      </c>
-      <c r="L97" s="11">
-        <v>0.79465857399999995</v>
-      </c>
-      <c r="M97" s="11">
-        <v>1.0491350000000001E-3</v>
-      </c>
-      <c r="N97" s="11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="98" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="B98" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="C98" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="D98" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="E98" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="F98" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="G98" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="H98" s="11">
-        <v>1391</v>
-      </c>
-      <c r="I98" s="11" t="s">
-        <v>206</v>
-      </c>
-      <c r="K98" s="11">
-        <v>4.54108906</v>
-      </c>
-      <c r="L98" s="11">
-        <v>1.045845913</v>
-      </c>
-      <c r="M98" s="11">
-        <v>9.6011999999999996E-4</v>
-      </c>
-      <c r="N98" s="11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="99" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="B99" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="C99" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="D99" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="E99" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="F99" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="G99" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="H99" s="11">
-        <v>1471</v>
-      </c>
-      <c r="I99" s="11" t="s">
-        <v>206</v>
-      </c>
-      <c r="K99" s="11">
-        <v>3.4727631090000002</v>
-      </c>
-      <c r="L99" s="11">
-        <v>-0.34334535900000002</v>
-      </c>
-      <c r="M99" s="11">
-        <v>0.31209340200000002</v>
-      </c>
-      <c r="N99" s="11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="100" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="B100" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="C100" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="D100" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="E100" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="F100" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="G100" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="H100" s="11">
-        <v>1544</v>
-      </c>
-      <c r="I100" s="11" t="s">
-        <v>206</v>
-      </c>
-      <c r="K100" s="11">
-        <v>2.0478127810000002</v>
-      </c>
-      <c r="L100" s="11">
-        <v>-0.50584207999999997</v>
-      </c>
-      <c r="M100" s="11">
-        <v>0.15445488299999999</v>
-      </c>
-      <c r="N100" s="11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="101" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="B101" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="C101" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="D101" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="E101" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="F101" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="G101" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="H101" s="11">
-        <v>1635</v>
-      </c>
-      <c r="I101" s="11" t="s">
-        <v>206</v>
-      </c>
-      <c r="K101" s="11">
-        <v>4.365137786</v>
-      </c>
-      <c r="L101" s="11">
-        <v>-0.31499556299999998</v>
-      </c>
-      <c r="M101" s="11">
-        <v>0.41762116399999999</v>
-      </c>
-      <c r="N101" s="11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="102" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="B102" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="C102" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="D102" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="E102" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="F102" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="G102" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="H102" s="11">
-        <v>1666</v>
-      </c>
-      <c r="I102" s="11" t="s">
-        <v>207</v>
-      </c>
-      <c r="K102" s="11">
-        <v>2.3021172179999998</v>
-      </c>
-      <c r="L102" s="11">
-        <v>-1.988707816</v>
-      </c>
-      <c r="M102" s="11">
-        <v>4.7900000000000002E-9</v>
-      </c>
-      <c r="N102" s="11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="103" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="B103" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="C103" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="D103" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="E103" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="F103" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="G103" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="H103" s="11">
-        <v>1810</v>
-      </c>
-      <c r="I103" s="11" t="s">
-        <v>206</v>
-      </c>
-      <c r="K103" s="11">
-        <v>4.7653295929999997</v>
-      </c>
-      <c r="L103" s="11">
-        <v>-1.7664919160000001</v>
-      </c>
-      <c r="M103" s="11">
-        <v>2.45E-9</v>
-      </c>
-      <c r="N103" s="11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="104" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="B104" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="C104" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="D104" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="E104" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="F104" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="G104" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="H104" s="11">
-        <v>1857</v>
-      </c>
-      <c r="I104" s="11" t="s">
-        <v>207</v>
-      </c>
-      <c r="K104" s="11">
-        <v>4.0173615600000003</v>
-      </c>
-      <c r="L104" s="11">
-        <v>5.0176947E-2</v>
-      </c>
-      <c r="M104" s="11">
-        <v>0.86246237800000003</v>
-      </c>
-      <c r="N104" s="11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="105" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="B105" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="C105" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="D105" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="E105" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="F105" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="G105" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="H105" s="11">
-        <v>1877</v>
-      </c>
-      <c r="I105" s="11" t="s">
-        <v>206</v>
-      </c>
-      <c r="K105" s="11">
-        <v>2.2494064869999999</v>
-      </c>
-      <c r="L105" s="11">
-        <v>-0.81070486399999997</v>
-      </c>
-      <c r="M105" s="11">
-        <v>1.3709555999999999E-2</v>
-      </c>
-      <c r="N105" s="11">
-        <v>2</v>
+    <row r="105" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A105" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="F105" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="G105" s="2" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.3">
@@ -5618,7 +5627,7 @@
         <v>179</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>186</v>
@@ -5641,7 +5650,7 @@
         <v>179</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>186</v>
@@ -5650,7 +5659,7 @@
         <v>184</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.3">
@@ -5664,7 +5673,7 @@
         <v>179</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>186</v>
@@ -5686,17 +5695,17 @@
       <c r="C109" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="D109" s="1" t="s">
-        <v>99</v>
+      <c r="D109" s="2" t="s">
+        <v>2</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>186</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.3">
@@ -5710,7 +5719,7 @@
         <v>179</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>186</v>
@@ -5719,7 +5728,7 @@
         <v>175</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.3">
@@ -5733,7 +5742,7 @@
         <v>179</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>186</v>
@@ -5756,13 +5765,13 @@
         <v>179</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>186</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>175</v>
+        <v>121</v>
       </c>
       <c r="G112" s="2" t="s">
         <v>183</v>
@@ -5779,13 +5788,13 @@
         <v>179</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>186</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>121</v>
+        <v>187</v>
       </c>
       <c r="G113" s="2" t="s">
         <v>183</v>
@@ -5802,13 +5811,13 @@
         <v>179</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="F114" s="2" t="s">
-        <v>187</v>
+      <c r="F114" s="5" t="s">
+        <v>175</v>
       </c>
       <c r="G114" s="2" t="s">
         <v>183</v>
@@ -5825,13 +5834,13 @@
         <v>179</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="F115" s="5" t="s">
-        <v>175</v>
+      <c r="F115" s="2" t="s">
+        <v>185</v>
       </c>
       <c r="G115" s="2" t="s">
         <v>183</v>
@@ -5848,13 +5857,13 @@
         <v>179</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="F116" s="2" t="s">
-        <v>185</v>
+      <c r="F116" s="5" t="s">
+        <v>175</v>
       </c>
       <c r="G116" s="2" t="s">
         <v>183</v>
@@ -5871,7 +5880,7 @@
         <v>179</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>186</v>
@@ -5894,13 +5903,13 @@
         <v>179</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="F118" s="5" t="s">
-        <v>175</v>
+      <c r="F118" s="2" t="s">
+        <v>185</v>
       </c>
       <c r="G118" s="2" t="s">
         <v>183</v>
@@ -5908,25 +5917,25 @@
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="B119" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="C119" s="2" t="s">
-        <v>179</v>
+        <v>100</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>102</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.3">
@@ -5940,7 +5949,7 @@
         <v>102</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>190</v>
@@ -5949,7 +5958,7 @@
         <v>175</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.3">
@@ -5963,7 +5972,7 @@
         <v>102</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>190</v>
@@ -5986,7 +5995,7 @@
         <v>102</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>190</v>
@@ -6009,7 +6018,7 @@
         <v>102</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>190</v>
@@ -6032,7 +6041,7 @@
         <v>102</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>190</v>
@@ -6055,7 +6064,7 @@
         <v>102</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>190</v>
@@ -6078,7 +6087,7 @@
         <v>102</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>190</v>
@@ -6101,7 +6110,7 @@
         <v>102</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>190</v>
@@ -6124,7 +6133,7 @@
         <v>102</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>190</v>
@@ -6138,16 +6147,16 @@
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="B129" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="C129" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>105</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>190</v>
@@ -6156,7 +6165,7 @@
         <v>175</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.3">
@@ -6170,7 +6179,7 @@
         <v>105</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>190</v>
@@ -6193,7 +6202,7 @@
         <v>105</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>190</v>
@@ -6216,7 +6225,7 @@
         <v>105</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>190</v>
@@ -6225,7 +6234,7 @@
         <v>175</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.3">
@@ -6239,7 +6248,7 @@
         <v>105</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>190</v>
@@ -6262,7 +6271,7 @@
         <v>105</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>190</v>
@@ -6285,7 +6294,7 @@
         <v>105</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>190</v>
@@ -6294,7 +6303,7 @@
         <v>175</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.3">
@@ -6308,7 +6317,7 @@
         <v>105</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>190</v>
@@ -6317,7 +6326,7 @@
         <v>175</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.3">
@@ -6331,7 +6340,7 @@
         <v>105</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>190</v>
@@ -6354,7 +6363,7 @@
         <v>105</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>190</v>
@@ -6368,16 +6377,16 @@
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>190</v>
@@ -6386,7 +6395,7 @@
         <v>175</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.3">
@@ -6400,7 +6409,7 @@
         <v>108</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>190</v>
@@ -6423,7 +6432,7 @@
         <v>108</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>190</v>
@@ -6432,7 +6441,7 @@
         <v>175</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.3">
@@ -6446,7 +6455,7 @@
         <v>108</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>190</v>
@@ -6455,7 +6464,7 @@
         <v>175</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.3">
@@ -6469,7 +6478,7 @@
         <v>108</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>190</v>
@@ -6492,7 +6501,7 @@
         <v>108</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>190</v>
@@ -6515,7 +6524,7 @@
         <v>108</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>190</v>
@@ -6524,7 +6533,7 @@
         <v>175</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.3">
@@ -6538,7 +6547,7 @@
         <v>108</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>190</v>
@@ -6547,7 +6556,7 @@
         <v>175</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.3">
@@ -6561,7 +6570,7 @@
         <v>108</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>190</v>
@@ -6570,7 +6579,7 @@
         <v>175</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.3">
@@ -6584,7 +6593,7 @@
         <v>108</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E148" s="2" t="s">
         <v>190</v>
@@ -6598,16 +6607,16 @@
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149" s="4" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E149" s="2" t="s">
         <v>190</v>
@@ -6616,7 +6625,7 @@
         <v>175</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.3">
@@ -6630,7 +6639,7 @@
         <v>111</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E150" s="2" t="s">
         <v>190</v>
@@ -6653,7 +6662,7 @@
         <v>111</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E151" s="2" t="s">
         <v>190</v>
@@ -6676,7 +6685,7 @@
         <v>111</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E152" s="2" t="s">
         <v>190</v>
@@ -6699,7 +6708,7 @@
         <v>111</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E153" s="2" t="s">
         <v>190</v>
@@ -6722,7 +6731,7 @@
         <v>111</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E154" s="2" t="s">
         <v>190</v>
@@ -6745,7 +6754,7 @@
         <v>111</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E155" s="2" t="s">
         <v>190</v>
@@ -6754,7 +6763,7 @@
         <v>175</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.3">
@@ -6768,7 +6777,7 @@
         <v>111</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E156" s="2" t="s">
         <v>190</v>
@@ -6791,7 +6800,7 @@
         <v>111</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E157" s="2" t="s">
         <v>190</v>
@@ -6814,7 +6823,7 @@
         <v>111</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>190</v>
@@ -6828,16 +6837,16 @@
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A159" s="4" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E159" s="2" t="s">
         <v>190</v>
@@ -6846,7 +6855,7 @@
         <v>175</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.3">
@@ -6860,7 +6869,7 @@
         <v>114</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E160" s="2" t="s">
         <v>190</v>
@@ -6869,7 +6878,7 @@
         <v>175</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.3">
@@ -6883,7 +6892,7 @@
         <v>114</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E161" s="2" t="s">
         <v>190</v>
@@ -6906,7 +6915,7 @@
         <v>114</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E162" s="2" t="s">
         <v>190</v>
@@ -6929,7 +6938,7 @@
         <v>114</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E163" s="2" t="s">
         <v>190</v>
@@ -6952,7 +6961,7 @@
         <v>114</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E164" s="2" t="s">
         <v>190</v>
@@ -6975,7 +6984,7 @@
         <v>114</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E165" s="2" t="s">
         <v>190</v>
@@ -6998,7 +7007,7 @@
         <v>114</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E166" s="2" t="s">
         <v>190</v>
@@ -7021,7 +7030,7 @@
         <v>114</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E167" s="2" t="s">
         <v>190</v>
@@ -7044,7 +7053,7 @@
         <v>114</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E168" s="2" t="s">
         <v>190</v>
@@ -7058,16 +7067,16 @@
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A169" s="4" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E169" s="2" t="s">
         <v>190</v>
@@ -7076,7 +7085,7 @@
         <v>175</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.3">
@@ -7090,7 +7099,7 @@
         <v>117</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E170" s="2" t="s">
         <v>190</v>
@@ -7099,7 +7108,7 @@
         <v>175</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.3">
@@ -7113,7 +7122,7 @@
         <v>117</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E171" s="2" t="s">
         <v>190</v>
@@ -7136,7 +7145,7 @@
         <v>117</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E172" s="2" t="s">
         <v>190</v>
@@ -7159,7 +7168,7 @@
         <v>117</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E173" s="2" t="s">
         <v>190</v>
@@ -7182,7 +7191,7 @@
         <v>117</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E174" s="2" t="s">
         <v>190</v>
@@ -7205,7 +7214,7 @@
         <v>117</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E175" s="2" t="s">
         <v>190</v>
@@ -7228,7 +7237,7 @@
         <v>117</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E176" s="2" t="s">
         <v>190</v>
@@ -7251,7 +7260,7 @@
         <v>117</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E177" s="2" t="s">
         <v>190</v>
@@ -7274,7 +7283,7 @@
         <v>117</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E178" s="2" t="s">
         <v>190</v>
@@ -7288,16 +7297,16 @@
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A179" s="4" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E179" s="2" t="s">
         <v>190</v>
@@ -7306,7 +7315,7 @@
         <v>175</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.3">
@@ -7320,7 +7329,7 @@
         <v>123</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E180" s="2" t="s">
         <v>190</v>
@@ -7329,7 +7338,7 @@
         <v>175</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.3">
@@ -7343,7 +7352,7 @@
         <v>123</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E181" s="2" t="s">
         <v>190</v>
@@ -7366,7 +7375,7 @@
         <v>123</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E182" s="2" t="s">
         <v>190</v>
@@ -7389,7 +7398,7 @@
         <v>123</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E183" s="2" t="s">
         <v>190</v>
@@ -7412,7 +7421,7 @@
         <v>123</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E184" s="2" t="s">
         <v>190</v>
@@ -7421,7 +7430,7 @@
         <v>175</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.3">
@@ -7435,7 +7444,7 @@
         <v>123</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E185" s="2" t="s">
         <v>190</v>
@@ -7458,7 +7467,7 @@
         <v>123</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E186" s="2" t="s">
         <v>190</v>
@@ -7467,7 +7476,7 @@
         <v>175</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.3">
@@ -7481,7 +7490,7 @@
         <v>123</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E187" s="2" t="s">
         <v>190</v>
@@ -7504,7 +7513,7 @@
         <v>123</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E188" s="2" t="s">
         <v>190</v>
@@ -7518,16 +7527,16 @@
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A189" s="4" t="s">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E189" s="2" t="s">
         <v>190</v>
@@ -7536,7 +7545,7 @@
         <v>175</v>
       </c>
       <c r="G189" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.3">
@@ -7550,7 +7559,7 @@
         <v>126</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E190" s="2" t="s">
         <v>190</v>
@@ -7559,7 +7568,7 @@
         <v>175</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.3">
@@ -7573,7 +7582,7 @@
         <v>126</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E191" s="2" t="s">
         <v>190</v>
@@ -7596,7 +7605,7 @@
         <v>126</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E192" s="2" t="s">
         <v>190</v>
@@ -7619,7 +7628,7 @@
         <v>126</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E193" s="2" t="s">
         <v>190</v>
@@ -7642,7 +7651,7 @@
         <v>126</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E194" s="2" t="s">
         <v>190</v>
@@ -7665,7 +7674,7 @@
         <v>126</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E195" s="2" t="s">
         <v>190</v>
@@ -7688,7 +7697,7 @@
         <v>126</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E196" s="2" t="s">
         <v>190</v>
@@ -7711,7 +7720,7 @@
         <v>126</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E197" s="2" t="s">
         <v>190</v>
@@ -7734,7 +7743,7 @@
         <v>126</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E198" s="2" t="s">
         <v>190</v>
@@ -7748,25 +7757,25 @@
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A199" s="4" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F199" s="2" t="s">
         <v>175</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.3">
@@ -7780,7 +7789,7 @@
         <v>129</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E200" s="2" t="s">
         <v>191</v>
@@ -7789,7 +7798,7 @@
         <v>175</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.3">
@@ -7803,7 +7812,7 @@
         <v>129</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E201" s="2" t="s">
         <v>191</v>
@@ -7826,13 +7835,13 @@
         <v>129</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E202" s="2" t="s">
         <v>191</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>175</v>
+        <v>192</v>
       </c>
       <c r="G202" s="2" t="s">
         <v>183</v>
@@ -7849,13 +7858,13 @@
         <v>129</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E203" s="2" t="s">
         <v>191</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>192</v>
+        <v>175</v>
       </c>
       <c r="G203" s="2" t="s">
         <v>183</v>
@@ -7872,7 +7881,7 @@
         <v>129</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E204" s="2" t="s">
         <v>191</v>
@@ -7881,7 +7890,7 @@
         <v>175</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.3">
@@ -7895,7 +7904,7 @@
         <v>129</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E205" s="2" t="s">
         <v>191</v>
@@ -7918,7 +7927,7 @@
         <v>129</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E206" s="2" t="s">
         <v>191</v>
@@ -7927,7 +7936,7 @@
         <v>175</v>
       </c>
       <c r="G206" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.3">
@@ -7941,7 +7950,7 @@
         <v>129</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E207" s="2" t="s">
         <v>191</v>
@@ -7964,7 +7973,7 @@
         <v>129</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E208" s="2" t="s">
         <v>191</v>
@@ -7978,25 +7987,25 @@
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A209" s="4" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E209" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>175</v>
+        <v>121</v>
       </c>
       <c r="G209" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.3">
@@ -8010,7 +8019,7 @@
         <v>120</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E210" s="2" t="s">
         <v>193</v>
@@ -8027,13 +8036,13 @@
         <v>118</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>119</v>
+        <v>188</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>120</v>
+        <v>189</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E211" s="2" t="s">
         <v>193</v>
@@ -8056,7 +8065,7 @@
         <v>189</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E212" s="2" t="s">
         <v>193</v>
@@ -8070,22 +8079,22 @@
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A213" s="4" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>188</v>
+        <v>131</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>189</v>
+        <v>132</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E213" s="2" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="G213" s="2" t="s">
         <v>181</v>
@@ -8102,7 +8111,7 @@
         <v>132</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E214" s="2" t="s">
         <v>190</v>
@@ -8111,21 +8120,21 @@
         <v>133</v>
       </c>
       <c r="G214" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A215" s="4" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E215" s="2" t="s">
         <v>190</v>
@@ -8134,7 +8143,7 @@
         <v>133</v>
       </c>
       <c r="G215" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.3">
@@ -8148,7 +8157,7 @@
         <v>136</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E216" s="2" t="s">
         <v>190</v>
@@ -8157,18 +8166,18 @@
         <v>133</v>
       </c>
       <c r="G216" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A217" s="4" t="s">
-        <v>134</v>
+        <v>115</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D217" s="2" t="s">
         <v>12</v>
@@ -8185,16 +8194,16 @@
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A218" s="4" t="s">
-        <v>115</v>
+        <v>139</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E218" s="2" t="s">
         <v>190</v>
@@ -8203,7 +8212,7 @@
         <v>133</v>
       </c>
       <c r="G218" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.3">
@@ -8217,7 +8226,7 @@
         <v>141</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E219" s="2" t="s">
         <v>190</v>
@@ -8226,21 +8235,21 @@
         <v>133</v>
       </c>
       <c r="G219" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A220" s="4" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E220" s="2" t="s">
         <v>190</v>
@@ -8249,7 +8258,7 @@
         <v>133</v>
       </c>
       <c r="G220" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.3">
@@ -8263,7 +8272,7 @@
         <v>144</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E221" s="2" t="s">
         <v>190</v>
@@ -8272,21 +8281,21 @@
         <v>133</v>
       </c>
       <c r="G221" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A222" s="4" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E222" s="2" t="s">
         <v>190</v>
@@ -8295,7 +8304,7 @@
         <v>133</v>
       </c>
       <c r="G222" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.3">
@@ -8309,7 +8318,7 @@
         <v>147</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E223" s="2" t="s">
         <v>190</v>
@@ -8318,21 +8327,21 @@
         <v>133</v>
       </c>
       <c r="G223" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A224" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E224" s="2" t="s">
         <v>190</v>
@@ -8341,7 +8350,7 @@
         <v>133</v>
       </c>
       <c r="G224" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.3">
@@ -8355,7 +8364,7 @@
         <v>150</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E225" s="2" t="s">
         <v>190</v>
@@ -8364,21 +8373,21 @@
         <v>133</v>
       </c>
       <c r="G225" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A226" s="4" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E226" s="2" t="s">
         <v>190</v>
@@ -8387,7 +8396,7 @@
         <v>133</v>
       </c>
       <c r="G226" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.3">
@@ -8401,7 +8410,7 @@
         <v>153</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E227" s="2" t="s">
         <v>190</v>
@@ -8410,21 +8419,21 @@
         <v>133</v>
       </c>
       <c r="G227" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A228" s="4" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E228" s="2" t="s">
         <v>190</v>
@@ -8433,7 +8442,7 @@
         <v>133</v>
       </c>
       <c r="G228" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.3">
@@ -8447,7 +8456,7 @@
         <v>156</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E229" s="2" t="s">
         <v>190</v>
@@ -8456,21 +8465,21 @@
         <v>133</v>
       </c>
       <c r="G229" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A230" s="4" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E230" s="2" t="s">
         <v>190</v>
@@ -8479,7 +8488,7 @@
         <v>133</v>
       </c>
       <c r="G230" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.3">
@@ -8493,7 +8502,7 @@
         <v>159</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E231" s="2" t="s">
         <v>190</v>
@@ -8502,21 +8511,21 @@
         <v>133</v>
       </c>
       <c r="G231" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A232" s="4" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E232" s="2" t="s">
         <v>190</v>
@@ -8525,7 +8534,7 @@
         <v>133</v>
       </c>
       <c r="G232" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.3">
@@ -8539,7 +8548,7 @@
         <v>162</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E233" s="2" t="s">
         <v>190</v>
@@ -8548,21 +8557,21 @@
         <v>133</v>
       </c>
       <c r="G233" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A234" s="4" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E234" s="2" t="s">
         <v>190</v>
@@ -8571,7 +8580,7 @@
         <v>133</v>
       </c>
       <c r="G234" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.3">
@@ -8585,7 +8594,7 @@
         <v>165</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E235" s="2" t="s">
         <v>190</v>
@@ -8594,21 +8603,21 @@
         <v>133</v>
       </c>
       <c r="G235" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A236" s="4" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E236" s="2" t="s">
         <v>190</v>
@@ -8617,7 +8626,7 @@
         <v>133</v>
       </c>
       <c r="G236" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.3">
@@ -8631,7 +8640,7 @@
         <v>168</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E237" s="2" t="s">
         <v>190</v>
@@ -8640,18 +8649,18 @@
         <v>133</v>
       </c>
       <c r="G237" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A238" s="4" t="s">
-        <v>166</v>
+        <v>109</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>167</v>
+        <v>110</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>168</v>
+        <v>111</v>
       </c>
       <c r="D238" s="2" t="s">
         <v>12</v>
@@ -8668,16 +8677,16 @@
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A239" s="4" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>110</v>
+        <v>170</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>111</v>
+        <v>171</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E239" s="2" t="s">
         <v>190</v>
@@ -8686,7 +8695,7 @@
         <v>133</v>
       </c>
       <c r="G239" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.3">
@@ -8700,7 +8709,7 @@
         <v>171</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E240" s="2" t="s">
         <v>190</v>
@@ -8709,34 +8718,11 @@
         <v>133</v>
       </c>
       <c r="G240" s="2" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A241" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="B241" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="C241" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="D241" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E241" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="F241" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="G241" s="2" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="1048575" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E1048575" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="1048574" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E1048574" s="2" t="s">
         <v>186</v>
       </c>
     </row>
